--- a/USCIS2025/Biling-USCIS-QA/resources/2025Questionscompared2008_CORRECTED.xlsx
+++ b/USCIS2025/Biling-USCIS-QA/resources/2025Questionscompared2008_CORRECTED.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\15857\Documents\GitHub\textenergy.github.io\USCIS2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\15857\Documents\GitHub\textenergy.github.io\USCIS2025\Biling-USCIS-QA\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500008CC-EF93-4A8C-B690-B5ABF7A055B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C621A8D1-5C0D-4798-8D66-188252D0BAF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="1950" windowWidth="19680" windowHeight="8535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="810" yWindow="765" windowWidth="19680" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025 vs 2008 Comparison" sheetId="1" r:id="rId1"/>
@@ -3477,7 +3477,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3505,6 +3505,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3537,7 +3543,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3624,6 +3630,15 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4003,7 +4018,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="32" t="s">
         <v>220</v>
       </c>
       <c r="B3" s="22" t="s">
@@ -4080,7 +4095,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="32" t="s">
         <v>220</v>
       </c>
       <c r="B8" s="22" t="s">
@@ -4153,7 +4168,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="32" t="s">
         <v>220</v>
       </c>
       <c r="B13" s="22" t="s">
@@ -4273,7 +4288,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="32" t="s">
         <v>220</v>
       </c>
       <c r="B21" s="5"/>
@@ -4417,7 +4432,7 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="32" t="s">
         <v>220</v>
       </c>
       <c r="B31" s="22" t="s">
@@ -4503,7 +4518,7 @@
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="32" t="s">
         <v>220</v>
       </c>
       <c r="B37" s="22" t="s">
@@ -4533,7 +4548,7 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="32" t="s">
         <v>220</v>
       </c>
       <c r="B39" s="22" t="s">
@@ -4550,7 +4565,7 @@
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="32" t="s">
         <v>220</v>
       </c>
       <c r="B40" s="22" t="s">
@@ -4625,7 +4640,7 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="32" t="s">
         <v>220</v>
       </c>
       <c r="B45" s="22" t="s">
@@ -4739,7 +4754,7 @@
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="32" t="s">
         <v>220</v>
       </c>
       <c r="B53" s="22" t="s">
@@ -4868,7 +4883,7 @@
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="32" t="s">
         <v>220</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -4945,7 +4960,7 @@
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="5" t="s">
+      <c r="A67" s="32" t="s">
         <v>220</v>
       </c>
       <c r="B67" s="22" t="s">
@@ -5059,7 +5074,7 @@
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="5" t="s">
+      <c r="A75" s="32" t="s">
         <v>220</v>
       </c>
       <c r="B75" s="22" t="s">
@@ -5119,7 +5134,7 @@
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="5" t="s">
+      <c r="A79" s="32" t="s">
         <v>220</v>
       </c>
       <c r="B79" s="22" t="s">
@@ -5237,7 +5252,7 @@
       </c>
     </row>
     <row r="87" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="5" t="s">
+      <c r="A87" s="32" t="s">
         <v>220</v>
       </c>
       <c r="B87" s="5"/>
@@ -5349,7 +5364,7 @@
       </c>
     </row>
     <row r="95" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="5" t="s">
+      <c r="A95" s="32" t="s">
         <v>220</v>
       </c>
       <c r="B95" s="22" t="s">
@@ -5614,7 +5629,7 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A114" s="5" t="s">
+      <c r="A114" s="32" t="s">
         <v>220</v>
       </c>
       <c r="B114" s="22" t="s">
@@ -5644,7 +5659,7 @@
       </c>
     </row>
     <row r="116" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A116" s="5" t="s">
+      <c r="A116" s="32" t="s">
         <v>220</v>
       </c>
       <c r="B116" s="22" t="s">
@@ -5732,7 +5747,7 @@
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="5" t="s">
+      <c r="A122" s="32" t="s">
         <v>220</v>
       </c>
       <c r="B122" s="22" t="s">
@@ -5805,7 +5820,7 @@
       </c>
     </row>
     <row r="127" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A127" s="5" t="s">
+      <c r="A127" s="32" t="s">
         <v>220</v>
       </c>
       <c r="B127" s="22" t="s">
@@ -5848,8 +5863,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E129">
-    <sortCondition ref="C2:C129"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E131">
+    <sortCondition ref="C2:C131"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="B3" location="'2008'!B1" display="Q001" xr:uid="{1A19114C-826E-41D2-84A0-1A887E0D388E}"/>
@@ -5974,7 +5989,7 @@
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.85546875" style="18" customWidth="1"/>
-    <col min="3" max="3" width="67.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="87.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="36.5703125" style="1" customWidth="1"/>
     <col min="5" max="5" width="32.42578125" style="1" customWidth="1"/>
     <col min="6" max="6" width="28.5703125" style="1" customWidth="1"/>
@@ -6104,10 +6119,10 @@
       <c r="A3" s="1">
         <v>2025</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="33" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="13" t="s">
@@ -6312,10 +6327,10 @@
       <c r="A8" s="1">
         <v>2025</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="33" t="s">
         <v>633</v>
       </c>
       <c r="D8" s="13" t="s">
@@ -6521,7 +6536,7 @@
       <c r="B13" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="33" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="13" t="s">
@@ -6857,7 +6872,7 @@
       <c r="B21" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="33" t="s">
         <v>1002</v>
       </c>
       <c r="D21" s="24" t="s">
@@ -7242,7 +7257,7 @@
       <c r="B31" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="33" t="s">
         <v>48</v>
       </c>
       <c r="D31" s="13" t="s">
@@ -7482,7 +7497,7 @@
       <c r="B37" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="33" t="s">
         <v>58</v>
       </c>
       <c r="D37" s="13" t="s">
@@ -7560,7 +7575,7 @@
       <c r="B39" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="33" t="s">
         <v>62</v>
       </c>
       <c r="D39" s="13" t="s">
@@ -7598,7 +7613,7 @@
       <c r="B40" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="33" t="s">
         <v>64</v>
       </c>
       <c r="D40" s="13" t="s">
@@ -7798,7 +7813,7 @@
       <c r="B45" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="33" t="s">
         <v>73</v>
       </c>
       <c r="D45" s="13" t="s">
@@ -8158,7 +8173,7 @@
       <c r="B53" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="33" t="s">
         <v>87</v>
       </c>
       <c r="D53" s="13" t="s">
@@ -8524,7 +8539,7 @@
       <c r="B62" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="C62" s="13" t="s">
+      <c r="C62" s="33" t="s">
         <v>105</v>
       </c>
       <c r="D62" s="13" t="s">
@@ -8732,7 +8747,7 @@
       <c r="B67" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="C67" s="33" t="s">
         <v>1012</v>
       </c>
       <c r="D67" s="13" t="s">
@@ -9096,7 +9111,7 @@
       <c r="B75" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="C75" s="13" t="s">
+      <c r="C75" s="33" t="s">
         <v>126</v>
       </c>
       <c r="D75" s="13" t="s">
@@ -9274,7 +9289,7 @@
       <c r="B79" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="C79" s="13" t="s">
+      <c r="C79" s="33" t="s">
         <v>134</v>
       </c>
       <c r="D79" s="13" t="s">
@@ -9626,7 +9641,7 @@
       <c r="B87" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="C87" s="24" t="s">
+      <c r="C87" s="33" t="s">
         <v>1016</v>
       </c>
       <c r="D87" s="24" t="s">
@@ -9980,7 +9995,7 @@
       <c r="B95" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="C95" s="13" t="s">
+      <c r="C95" s="33" t="s">
         <v>1083</v>
       </c>
       <c r="D95" s="13" t="s">
@@ -10763,7 +10778,7 @@
       <c r="B114" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="C114" s="13" t="s">
+      <c r="C114" s="33" t="s">
         <v>1023</v>
       </c>
       <c r="D114" s="13" t="s">
@@ -10843,7 +10858,7 @@
       <c r="B116" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="C116" s="13" t="s">
+      <c r="C116" s="33" t="s">
         <v>197</v>
       </c>
       <c r="D116" s="13" t="s">
@@ -11143,7 +11158,7 @@
       <c r="B122" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="C122" s="13" t="s">
+      <c r="C122" s="33" t="s">
         <v>207</v>
       </c>
       <c r="D122" s="13" t="s">
@@ -11341,7 +11356,7 @@
       <c r="B127" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="C127" s="13" t="s">
+      <c r="C127" s="33" t="s">
         <v>1027</v>
       </c>
       <c r="D127" s="13" t="s">
